--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754912235_individual_h_6.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754912235_individual_h_6.xlsx
@@ -658,7 +658,7 @@
         <v>0.008454177761639635</v>
       </c>
       <c r="C2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>27513963</v>
+        <v>4250307</v>
       </c>
       <c r="L2" t="n">
-        <v>15858308</v>
+        <v>2195904</v>
       </c>
       <c r="M2" t="n">
-        <v>3775322</v>
+        <v>491265</v>
       </c>
       <c r="N2" t="n">
-        <v>166736</v>
+        <v>16096</v>
       </c>
       <c r="O2" t="n">
-        <v>2196268</v>
+        <v>285280</v>
       </c>
       <c r="P2" t="n">
-        <v>876151</v>
+        <v>120441</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9998964667320251</v>
+        <v>0.9999027252197266</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8978642821311951</v>
+        <v>0.8244026899337769</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7971778512001038</v>
+        <v>0.6676803827285767</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7481138110160828</v>
+        <v>0.5794893503189087</v>
       </c>
       <c r="U2" t="n">
-        <v>0.234213650226593</v>
+        <v>0.1331733763217926</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7875199913978577</v>
+        <v>0.6431033611297607</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8659595251083374</v>
+        <v>0.7559975981712341</v>
       </c>
       <c r="X2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>28872412</v>
+        <v>4796855</v>
       </c>
       <c r="AG2" t="n">
-        <v>17836630</v>
+        <v>2983951</v>
       </c>
       <c r="AH2" t="n">
-        <v>4798928</v>
+        <v>801380</v>
       </c>
       <c r="AI2" t="n">
-        <v>353991</v>
+        <v>59049</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2755108</v>
+        <v>459641</v>
       </c>
       <c r="AK2" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9564692974090576</v>
+        <v>0.9560109972953796</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113166332244873</v>
+        <v>0.9115679264068604</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581637144088745</v>
+        <v>0.8585426211357117</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6622001528739929</v>
+        <v>0.6615541577339172</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020119309425354</v>
+        <v>0.9020492434501648</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314349889755249</v>
+        <v>0.9314607977867126</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002027047184025982</v>
       </c>
       <c r="C3" t="n">
-        <v>1212</v>
+        <v>207</v>
       </c>
       <c r="D3" t="n">
-        <v>27513963</v>
+        <v>4250307</v>
       </c>
       <c r="E3" t="n">
-        <v>2590942</v>
+        <v>739504</v>
       </c>
       <c r="F3" t="n">
-        <v>39444</v>
+        <v>17078</v>
       </c>
       <c r="G3" t="n">
-        <v>4559</v>
+        <v>1594</v>
       </c>
       <c r="H3" t="n">
-        <v>1937</v>
+        <v>893</v>
       </c>
       <c r="I3" t="n">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="J3" t="n">
-        <v>60095810</v>
+        <v>10016008</v>
       </c>
       <c r="K3" t="n">
-        <v>64695627</v>
+        <v>10414679</v>
       </c>
       <c r="L3" t="n">
-        <v>74342413</v>
+        <v>11957391</v>
       </c>
       <c r="M3" t="n">
-        <v>91110139</v>
+        <v>15038077</v>
       </c>
       <c r="N3" t="n">
-        <v>96897448</v>
+        <v>16135487</v>
       </c>
       <c r="O3" t="n">
-        <v>94329222</v>
+        <v>15661342</v>
       </c>
       <c r="P3" t="n">
-        <v>96681957</v>
+        <v>16097287</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.912504255771637</v>
+        <v>0.8484310507774353</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8090794086456299</v>
+        <v>0.6696344017982483</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6746068596839905</v>
+        <v>0.5253985524177551</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3116613030433655</v>
+        <v>0.1801575869321823</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7187199592590332</v>
+        <v>0.559439480304718</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7552863359451294</v>
+        <v>0.6226271986961365</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>28872412</v>
+        <v>4796855</v>
       </c>
       <c r="Z3" t="n">
-        <v>1187392</v>
+        <v>197460</v>
       </c>
       <c r="AA3" t="n">
-        <v>51135</v>
+        <v>8429</v>
       </c>
       <c r="AB3" t="n">
-        <v>40793</v>
+        <v>6823</v>
       </c>
       <c r="AC3" t="n">
-        <v>236</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>60099732</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>66511414</v>
+        <v>11099274</v>
       </c>
       <c r="AG3" t="n">
-        <v>76641422</v>
+        <v>12760866</v>
       </c>
       <c r="AH3" t="n">
-        <v>91588110</v>
+        <v>15262528</v>
       </c>
       <c r="AI3" t="n">
-        <v>97262032</v>
+        <v>16210047</v>
       </c>
       <c r="AJ3" t="n">
-        <v>94622500</v>
+        <v>15769750</v>
       </c>
       <c r="AK3" t="n">
-        <v>96738050</v>
+        <v>16122905</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575573801994324</v>
+        <v>0.9575310349464417</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100120067596436</v>
+        <v>0.9099469780921936</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8575135469436646</v>
+        <v>0.8570606708526611</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6616765260696411</v>
+        <v>0.660917341709137</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015980958938599</v>
+        <v>0.9013646841049194</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312928318977356</v>
+        <v>0.9312344789505005</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03199143872576704</v>
       </c>
       <c r="C4" t="n">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>2940883</v>
+        <v>851691</v>
       </c>
       <c r="E4" t="n">
-        <v>15858308</v>
+        <v>2195904</v>
       </c>
       <c r="F4" t="n">
-        <v>720580</v>
+        <v>199476</v>
       </c>
       <c r="G4" t="n">
-        <v>33519</v>
+        <v>11881</v>
       </c>
       <c r="H4" t="n">
-        <v>43209</v>
+        <v>18407</v>
       </c>
       <c r="I4" t="n">
-        <v>3832</v>
+        <v>1860</v>
       </c>
       <c r="J4" t="n">
-        <v>3922</v>
+        <v>614</v>
       </c>
       <c r="K4" t="n">
-        <v>3129825</v>
+        <v>905313</v>
       </c>
       <c r="L4" t="n">
-        <v>4034753</v>
+        <v>1092951</v>
       </c>
       <c r="M4" t="n">
-        <v>1271132</v>
+        <v>356490</v>
       </c>
       <c r="N4" t="n">
-        <v>545161</v>
+        <v>104769</v>
       </c>
       <c r="O4" t="n">
-        <v>592573</v>
+        <v>158319</v>
       </c>
       <c r="P4" t="n">
-        <v>135618</v>
+        <v>38873</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999482035636902</v>
+        <v>0.9999513626098633</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9051250815391541</v>
+        <v>0.8362442851066589</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8030845522880554</v>
+        <v>0.6686559319496155</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7094614505767822</v>
+        <v>0.5511199235916138</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2674434185028076</v>
+        <v>0.1531428247690201</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7515487670898438</v>
+        <v>0.5983611345291138</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8068453669548035</v>
+        <v>0.6828611493110657</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1226769</v>
+        <v>206052</v>
       </c>
       <c r="Z4" t="n">
-        <v>17836630</v>
+        <v>2983951</v>
       </c>
       <c r="AA4" t="n">
-        <v>496804</v>
+        <v>82537</v>
       </c>
       <c r="AB4" t="n">
-        <v>32965</v>
+        <v>5520</v>
       </c>
       <c r="AC4" t="n">
-        <v>6858</v>
+        <v>1130</v>
       </c>
       <c r="AD4" t="n">
-        <v>408</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1314038</v>
+        <v>220718</v>
       </c>
       <c r="AG4" t="n">
-        <v>1735744</v>
+        <v>289476</v>
       </c>
       <c r="AH4" t="n">
-        <v>793161</v>
+        <v>132039</v>
       </c>
       <c r="AI4" t="n">
-        <v>180577</v>
+        <v>30209</v>
       </c>
       <c r="AJ4" t="n">
-        <v>299295</v>
+        <v>49911</v>
       </c>
       <c r="AK4" t="n">
-        <v>79525</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570130109786987</v>
+        <v>0.9567704200744629</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910663902759552</v>
+        <v>0.9107567667961121</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.85783851146698</v>
+        <v>0.8578009605407715</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6619382500648499</v>
+        <v>0.6612355709075928</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018049240112305</v>
+        <v>0.9017068147659302</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313638806343079</v>
+        <v>0.9313476085662842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1135</v>
+        <v>196</v>
       </c>
       <c r="D5" t="n">
-        <v>121424</v>
+        <v>36778</v>
       </c>
       <c r="E5" t="n">
-        <v>1240230</v>
+        <v>295691</v>
       </c>
       <c r="F5" t="n">
-        <v>3775322</v>
+        <v>491265</v>
       </c>
       <c r="G5" t="n">
-        <v>194449</v>
+        <v>33421</v>
       </c>
       <c r="H5" t="n">
-        <v>243532</v>
+        <v>69543</v>
       </c>
       <c r="I5" t="n">
-        <v>20237</v>
+        <v>8139</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2638185</v>
+        <v>759301</v>
       </c>
       <c r="L5" t="n">
-        <v>3742126</v>
+        <v>1083354</v>
       </c>
       <c r="M5" t="n">
-        <v>1821007</v>
+        <v>443768</v>
       </c>
       <c r="N5" t="n">
-        <v>368255</v>
+        <v>73248</v>
       </c>
       <c r="O5" t="n">
-        <v>859537</v>
+        <v>224659</v>
       </c>
       <c r="P5" t="n">
-        <v>283874</v>
+        <v>72999</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999599456787109</v>
+        <v>0.9999623894691467</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9411293268203735</v>
+        <v>0.8980615735054016</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9206259250640869</v>
+        <v>0.8667263984680176</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9684403538703918</v>
+        <v>0.9509934186935425</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9906772971153259</v>
+        <v>0.9890984892845154</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9851791858673096</v>
+        <v>0.9765470027923584</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9957184791564941</v>
+        <v>0.9931491017341614</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>48155</v>
+        <v>8093</v>
       </c>
       <c r="Z5" t="n">
-        <v>510890</v>
+        <v>85757</v>
       </c>
       <c r="AA5" t="n">
-        <v>4798928</v>
+        <v>801380</v>
       </c>
       <c r="AB5" t="n">
-        <v>59714</v>
+        <v>9985</v>
       </c>
       <c r="AC5" t="n">
-        <v>174844</v>
+        <v>29185</v>
       </c>
       <c r="AD5" t="n">
-        <v>3798</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1279736</v>
+        <v>212753</v>
       </c>
       <c r="AG5" t="n">
-        <v>1763804</v>
+        <v>295307</v>
       </c>
       <c r="AH5" t="n">
-        <v>797401</v>
+        <v>133653</v>
       </c>
       <c r="AI5" t="n">
-        <v>181000</v>
+        <v>30295</v>
       </c>
       <c r="AJ5" t="n">
-        <v>300697</v>
+        <v>50298</v>
       </c>
       <c r="AK5" t="n">
-        <v>79702</v>
+        <v>13302</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735268950462341</v>
+        <v>0.9734548926353455</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642821550369263</v>
+        <v>0.9641887545585632</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837660789489746</v>
+        <v>0.9837294220924377</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963095784187317</v>
+        <v>0.9962948560714722</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938762187957764</v>
+        <v>0.9938633441925049</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998374879360199</v>
+        <v>0.9983736872673035</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>214</v>
+        <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>65503</v>
+        <v>15477</v>
       </c>
       <c r="E6" t="n">
-        <v>120899</v>
+        <v>21163</v>
       </c>
       <c r="F6" t="n">
-        <v>124912</v>
+        <v>25788</v>
       </c>
       <c r="G6" t="n">
-        <v>166736</v>
+        <v>16096</v>
       </c>
       <c r="H6" t="n">
-        <v>53055</v>
+        <v>9641</v>
       </c>
       <c r="I6" t="n">
-        <v>3672</v>
+        <v>1147</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>38779</v>
+        <v>6517</v>
       </c>
       <c r="Z6" t="n">
-        <v>32116</v>
+        <v>5368</v>
       </c>
       <c r="AA6" t="n">
-        <v>65335</v>
+        <v>10940</v>
       </c>
       <c r="AB6" t="n">
-        <v>353991</v>
+        <v>59049</v>
       </c>
       <c r="AC6" t="n">
-        <v>41884</v>
+        <v>6989</v>
       </c>
       <c r="AD6" t="n">
-        <v>2886</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>243</v>
+        <v>40</v>
       </c>
       <c r="D7" t="n">
-        <v>1815</v>
+        <v>1312</v>
       </c>
       <c r="E7" t="n">
-        <v>78260</v>
+        <v>34262</v>
       </c>
       <c r="F7" t="n">
-        <v>370854</v>
+        <v>107720</v>
       </c>
       <c r="G7" t="n">
-        <v>300579</v>
+        <v>53623</v>
       </c>
       <c r="H7" t="n">
-        <v>2196268</v>
+        <v>285280</v>
       </c>
       <c r="I7" t="n">
-        <v>107786</v>
+        <v>27702</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>167</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4860</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>177905</v>
+        <v>29802</v>
       </c>
       <c r="AB7" t="n">
-        <v>45512</v>
+        <v>7615</v>
       </c>
       <c r="AC7" t="n">
-        <v>2755108</v>
+        <v>459641</v>
       </c>
       <c r="AD7" t="n">
-        <v>72253</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1015</v>
+        <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>200</v>
+        <v>55</v>
       </c>
       <c r="E8" t="n">
-        <v>4422</v>
+        <v>2331</v>
       </c>
       <c r="F8" t="n">
-        <v>15342</v>
+        <v>6428</v>
       </c>
       <c r="G8" t="n">
-        <v>12055</v>
+        <v>4250</v>
       </c>
       <c r="H8" t="n">
-        <v>250840</v>
+        <v>59835</v>
       </c>
       <c r="I8" t="n">
-        <v>876151</v>
+        <v>120441</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>486</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1982</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1593</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>75473</v>
+        <v>12596</v>
       </c>
       <c r="AD8" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
